--- a/outputs/55965.xlsx
+++ b/outputs/55965.xlsx
@@ -186,7 +186,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -194,11 +194,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -214,19 +214,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -523,7 +523,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="2" width="2.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -540,7 +540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J2" s="2" t="s">
         <v>2</v>
       </c>
@@ -548,7 +548,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
@@ -556,7 +556,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J4" s="2" t="s">
         <v>4</v>
       </c>
@@ -564,7 +564,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J5" s="2" t="s">
         <v>5</v>
       </c>
@@ -572,7 +572,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J6" s="2" t="s">
         <v>3</v>
       </c>
@@ -580,7 +580,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J7" s="2" t="s">
         <v>6</v>
       </c>
@@ -588,7 +588,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J8" s="2" t="s">
         <v>7</v>
       </c>
@@ -596,7 +596,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J9" s="2" t="s">
         <v>2</v>
       </c>
@@ -604,7 +604,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J10" s="2" t="s">
         <v>6</v>
       </c>
@@ -612,7 +612,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J11" s="2" t="s">
         <v>3</v>
       </c>
@@ -620,7 +620,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J12" s="2" t="s">
         <v>5</v>
       </c>
@@ -628,7 +628,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J13" s="2" t="s">
         <v>8</v>
       </c>
@@ -636,7 +636,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J14" s="2" t="s">
         <v>9</v>
       </c>
@@ -644,7 +644,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J15" s="2" t="s">
         <v>3</v>
       </c>
@@ -652,7 +652,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J16" s="2" t="s">
         <v>10</v>
       </c>
@@ -660,7 +660,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J17" s="2" t="s">
         <v>11</v>
       </c>
@@ -668,7 +668,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J18" s="2" t="s">
         <v>3</v>
       </c>
@@ -676,7 +676,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J19" s="2" t="s">
         <v>6</v>
       </c>
@@ -684,7 +684,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J20" s="2" t="s">
         <v>12</v>
       </c>
@@ -692,7 +692,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J21" s="2" t="s">
         <v>2</v>
       </c>
@@ -700,7 +700,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J22" s="2" t="s">
         <v>3</v>
       </c>
@@ -708,7 +708,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J23" s="2" t="s">
         <v>4</v>
       </c>
@@ -716,7 +716,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J24" s="2" t="s">
         <v>2</v>
       </c>
@@ -724,7 +724,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J25" s="2" t="s">
         <v>6</v>
       </c>
@@ -732,7 +732,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J26" s="2" t="s">
         <v>13</v>
       </c>
@@ -740,7 +740,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J27" s="2" t="s">
         <v>14</v>
       </c>
@@ -748,7 +748,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J28" s="2" t="s">
         <v>15</v>
       </c>
@@ -756,7 +756,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J29" s="2" t="s">
         <v>4</v>
       </c>
@@ -764,7 +764,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J30" s="6" t="s">
         <v>5</v>
       </c>
@@ -772,7 +772,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J31" s="7" t="s">
         <v>8</v>
       </c>
@@ -780,7 +780,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J32" s="7" t="s">
         <v>7</v>
       </c>
@@ -788,7 +788,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J33" s="7" t="s">
         <v>5</v>
       </c>
@@ -796,7 +796,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J34" s="2" t="s">
         <v>2</v>
       </c>
@@ -804,7 +804,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J35" s="2" t="s">
         <v>16</v>
       </c>
@@ -812,7 +812,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J36" s="2" t="s">
         <v>2</v>
       </c>
@@ -820,7 +820,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J37" s="2" t="s">
         <v>17</v>
       </c>
@@ -828,7 +828,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J38" s="2" t="s">
         <v>5</v>
       </c>
@@ -836,7 +836,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J39" s="2" t="s">
         <v>5</v>
       </c>
@@ -844,7 +844,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J40" s="2" t="s">
         <v>5</v>
       </c>
@@ -852,7 +852,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J41" s="2" t="s">
         <v>2</v>
       </c>
@@ -860,7 +860,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J42" s="2" t="s">
         <v>5</v>
       </c>
@@ -868,7 +868,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J43" s="2" t="s">
         <v>8</v>
       </c>
@@ -876,7 +876,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J44" s="2" t="s">
         <v>4</v>
       </c>
@@ -884,7 +884,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J45" s="2" t="s">
         <v>18</v>
       </c>
@@ -892,7 +892,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J46" s="2" t="s">
         <v>3</v>
       </c>
@@ -900,7 +900,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J47" s="2" t="s">
         <v>7</v>
       </c>
@@ -908,7 +908,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J48" s="2" t="s">
         <v>4</v>
       </c>
@@ -916,7 +916,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J49" s="2" t="s">
         <v>2</v>
       </c>
@@ -924,7 +924,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J50" s="2" t="s">
         <v>8</v>
       </c>
@@ -932,7 +932,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J51" s="2" t="s">
         <v>5</v>
       </c>
@@ -940,7 +940,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J52" s="2" t="s">
         <v>5</v>
       </c>
@@ -948,7 +948,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J53" s="2" t="s">
         <v>6</v>
       </c>
@@ -956,7 +956,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J54" s="6" t="s">
         <v>11</v>
       </c>
@@ -964,7 +964,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J55" s="6" t="s">
         <v>3</v>
       </c>
@@ -972,7 +972,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J56" s="6" t="s">
         <v>2</v>
       </c>
@@ -980,7 +980,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J57" s="6" t="s">
         <v>7</v>
       </c>
@@ -988,7 +988,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J58" s="6" t="s">
         <v>19</v>
       </c>
@@ -996,7 +996,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J59" s="6" t="s">
         <v>3</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J60" s="6" t="s">
         <v>4</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J61" s="6" t="s">
         <v>10</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J62" s="6" t="s">
         <v>20</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J63" s="2" t="s">
         <v>2</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J64" s="2" t="s">
         <v>11</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J65" s="2" t="s">
         <v>6</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J66" s="2" t="s">
         <v>6</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J67" s="2" t="s">
         <v>5</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J68" s="2" t="s">
         <v>2</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J69" s="2" t="s">
         <v>4</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J70" s="2" t="s">
         <v>5</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J71" s="2" t="s">
         <v>5</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J72" s="7" t="s">
         <v>18</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J73" s="7" t="s">
         <v>4</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J74" s="7" t="s">
         <v>6</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J75" s="7" t="s">
         <v>11</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J76" s="7" t="s">
         <v>5</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J77" s="7" t="s">
         <v>4</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J78" s="7" t="s">
         <v>8</v>
       </c>
@@ -1188,7 +1188,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="9.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>44271.2708333333</v>
       </c>
@@ -1237,47 +1237,47 @@
         <v>330</v>
       </c>
       <c r="G2" s="10" t="str">
-        <f aca="false" t="array" ref="G2:G2">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E2,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J31</f>
         <v>2-2</v>
       </c>
       <c r="H2" s="10" t="str">
-        <f aca="false" t="array" ref="H2:H2">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E2,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J32</f>
         <v>3-2</v>
       </c>
       <c r="I2" s="10" t="str">
-        <f aca="false" t="array" ref="I2:I2">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E2,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J33</f>
         <v>0-0</v>
       </c>
       <c r="J2" s="10" t="str">
-        <f aca="false" t="array" ref="J2:J2">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E2,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J72</f>
         <v>5-2</v>
       </c>
       <c r="K2" s="10" t="str">
-        <f aca="false" t="array" ref="K2:K2">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E2,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J73</f>
         <v>1-0</v>
       </c>
       <c r="L2" s="10" t="str">
-        <f aca="false" t="array" ref="L2:L2">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E2,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J74</f>
         <v>2-1</v>
       </c>
       <c r="M2" s="10" t="str">
-        <f aca="false" t="array" ref="M2:M2">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E2,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J75</f>
         <v>3-1</v>
       </c>
       <c r="N2" s="10" t="str">
-        <f aca="false" t="array" ref="N2:N2">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E2,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J76</f>
         <v>0-0</v>
       </c>
       <c r="O2" s="10" t="str">
-        <f aca="false" t="array" ref="O2:O2">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E2,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J77</f>
         <v>1-0</v>
       </c>
       <c r="P2" s="10" t="str">
-        <f aca="false" t="array" ref="P2:P2">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E2,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J78</f>
         <v>2-2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>44271.3333333333</v>
       </c>
@@ -1285,47 +1285,47 @@
         <v>320</v>
       </c>
       <c r="G3" s="11" t="str">
-        <f aca="false" t="array" ref="G3:G3">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E3,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J30</f>
         <v>0-0</v>
       </c>
       <c r="H3" s="11" t="str">
-        <f aca="false" t="array" ref="H3:H3">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E3,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J54</f>
         <v>3-1</v>
       </c>
       <c r="I3" s="11" t="str">
-        <f aca="false" t="array" ref="I3:I3">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E3,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J55</f>
         <v>2-0</v>
       </c>
       <c r="J3" s="11" t="str">
-        <f aca="false" t="array" ref="J3:J3">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E3,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J56</f>
         <v>1-1</v>
       </c>
       <c r="K3" s="11" t="str">
-        <f aca="false" t="array" ref="K3:K3">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E3,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J57</f>
         <v>3-2</v>
       </c>
       <c r="L3" s="11" t="str">
-        <f aca="false" t="array" ref="L3:L3">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E3,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J58</f>
         <v>15-7</v>
       </c>
       <c r="M3" s="11" t="str">
-        <f aca="false" t="array" ref="M3:M3">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E3,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J59</f>
         <v>2-0</v>
       </c>
       <c r="N3" s="11" t="str">
-        <f aca="false" t="array" ref="N3:N3">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E3,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J60</f>
         <v>1-0</v>
       </c>
       <c r="O3" s="11" t="str">
-        <f aca="false" t="array" ref="O3:O3">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E3,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J61</f>
         <v>3-0</v>
       </c>
       <c r="P3" s="11" t="str">
-        <f aca="false" t="array" ref="P3:P3">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E3,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J62</f>
         <v>4-1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>44271.375</v>
       </c>
@@ -1333,47 +1333,47 @@
         <v>330</v>
       </c>
       <c r="G4" s="2" t="str">
-        <f aca="false" t="array" ref="G4:G4">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E4,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J31</f>
         <v>2-2</v>
       </c>
       <c r="H4" s="2" t="str">
-        <f aca="false" t="array" ref="H4:H4">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E4,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J32</f>
         <v>3-2</v>
       </c>
       <c r="I4" s="2" t="str">
-        <f aca="false" t="array" ref="I4:I4">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E4,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J33</f>
         <v>0-0</v>
       </c>
       <c r="J4" s="2" t="str">
-        <f aca="false" t="array" ref="J4:J4">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E4,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J72</f>
         <v>5-2</v>
       </c>
       <c r="K4" s="2" t="str">
-        <f aca="false" t="array" ref="K4:K4">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E4,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J73</f>
         <v>1-0</v>
       </c>
       <c r="L4" s="2" t="str">
-        <f aca="false" t="array" ref="L4:L4">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E4,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J74</f>
         <v>2-1</v>
       </c>
       <c r="M4" s="2" t="str">
-        <f aca="false" t="array" ref="M4:M4">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E4,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J75</f>
         <v>3-1</v>
       </c>
       <c r="N4" s="2" t="str">
-        <f aca="false" t="array" ref="N4:N4">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E4,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J76</f>
         <v>0-0</v>
       </c>
       <c r="O4" s="2" t="str">
-        <f aca="false" t="array" ref="O4:O4">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E4,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J77</f>
         <v>1-0</v>
       </c>
       <c r="P4" s="2" t="str">
-        <f aca="false" t="array" ref="P4:P4">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E4,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J78</f>
         <v>2-2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>44271.375</v>
       </c>
@@ -1381,47 +1381,47 @@
         <v>340</v>
       </c>
       <c r="G5" s="2" t="str">
-        <f aca="false" t="array" ref="G5:G5">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E5,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J29</f>
         <v>1-0</v>
       </c>
       <c r="H5" s="2" t="str">
-        <f aca="false" t="array" ref="H5:H5">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E5,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J63</f>
         <v>1-1</v>
       </c>
       <c r="I5" s="2" t="str">
-        <f aca="false" t="array" ref="I5:I5">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E5,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J64</f>
         <v>3-1</v>
       </c>
       <c r="J5" s="2" t="str">
-        <f aca="false" t="array" ref="J5:J5">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E5,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J65</f>
         <v>2-1</v>
       </c>
       <c r="K5" s="2" t="str">
-        <f aca="false" t="array" ref="K5:K5">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E5,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J66</f>
         <v>2-1</v>
       </c>
       <c r="L5" s="2" t="str">
-        <f aca="false" t="array" ref="L5:L5">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E5,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J67</f>
         <v>0-0</v>
       </c>
       <c r="M5" s="2" t="str">
-        <f aca="false" t="array" ref="M5:M5">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E5,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J68</f>
         <v>1-1</v>
       </c>
       <c r="N5" s="2" t="str">
-        <f aca="false" t="array" ref="N5:N5">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E5,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J69</f>
         <v>1-0</v>
       </c>
       <c r="O5" s="2" t="str">
-        <f aca="false" t="array" ref="O5:O5">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E5,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J70</f>
         <v>0-0</v>
       </c>
       <c r="P5" s="2" t="str">
-        <f aca="false" t="array" ref="P5:P5">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E5,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
-        <v>0-0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">DATI!J71</f>
+        <v>0-0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>44271.3958333333</v>
       </c>
@@ -1429,47 +1429,47 @@
         <v>350</v>
       </c>
       <c r="G6" s="2" t="str">
-        <f aca="false" t="array" ref="G6:G6">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E6,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J44</f>
         <v>1-0</v>
       </c>
       <c r="H6" s="2" t="str">
-        <f aca="false" t="array" ref="H6:H6">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E6,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J45</f>
         <v>5-2</v>
       </c>
       <c r="I6" s="2" t="str">
-        <f aca="false" t="array" ref="I6:I6">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E6,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J46</f>
         <v>2-0</v>
       </c>
       <c r="J6" s="2" t="str">
-        <f aca="false" t="array" ref="J6:J6">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E6,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J47</f>
         <v>3-2</v>
       </c>
       <c r="K6" s="2" t="str">
-        <f aca="false" t="array" ref="K6:K6">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E6,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J48</f>
         <v>1-0</v>
       </c>
       <c r="L6" s="2" t="str">
-        <f aca="false" t="array" ref="L6:L6">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E6,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J49</f>
         <v>1-1</v>
       </c>
       <c r="M6" s="2" t="str">
-        <f aca="false" t="array" ref="M6:M6">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E6,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J50</f>
         <v>2-2</v>
       </c>
       <c r="N6" s="2" t="str">
-        <f aca="false" t="array" ref="N6:N6">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E6,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J51</f>
         <v>0-0</v>
       </c>
       <c r="O6" s="2" t="str">
-        <f aca="false" t="array" ref="O6:O6">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E6,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J52</f>
         <v>0-0</v>
       </c>
       <c r="P6" s="2" t="str">
-        <f aca="false" t="array" ref="P6:P6">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E6,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J53</f>
         <v>2-1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>44271.40625</v>
       </c>
@@ -1477,47 +1477,47 @@
         <v>320</v>
       </c>
       <c r="G7" s="2" t="str">
-        <f aca="false" t="array" ref="G7:G7">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E7,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J30</f>
         <v>0-0</v>
       </c>
       <c r="H7" s="2" t="str">
-        <f aca="false" t="array" ref="H7:H7">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E7,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J54</f>
         <v>3-1</v>
       </c>
       <c r="I7" s="2" t="str">
-        <f aca="false" t="array" ref="I7:I7">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E7,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J55</f>
         <v>2-0</v>
       </c>
       <c r="J7" s="2" t="str">
-        <f aca="false" t="array" ref="J7:J7">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E7,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J56</f>
         <v>1-1</v>
       </c>
       <c r="K7" s="2" t="str">
-        <f aca="false" t="array" ref="K7:K7">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E7,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J57</f>
         <v>3-2</v>
       </c>
       <c r="L7" s="2" t="str">
-        <f aca="false" t="array" ref="L7:L7">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E7,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J58</f>
         <v>15-7</v>
       </c>
       <c r="M7" s="2" t="str">
-        <f aca="false" t="array" ref="M7:M7">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E7,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J59</f>
         <v>2-0</v>
       </c>
       <c r="N7" s="2" t="str">
-        <f aca="false" t="array" ref="N7:N7">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E7,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J60</f>
         <v>1-0</v>
       </c>
       <c r="O7" s="2" t="str">
-        <f aca="false" t="array" ref="O7:O7">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E7,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J61</f>
         <v>3-0</v>
       </c>
       <c r="P7" s="2" t="str">
-        <f aca="false" t="array" ref="P7:P7">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E7,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J62</f>
         <v>4-1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -1525,47 +1525,47 @@
         <v>330</v>
       </c>
       <c r="G8" s="2" t="str">
-        <f aca="false" t="array" ref="G8:G8">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E8,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J31</f>
         <v>2-2</v>
       </c>
       <c r="H8" s="2" t="str">
-        <f aca="false" t="array" ref="H8:H8">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E8,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J32</f>
         <v>3-2</v>
       </c>
       <c r="I8" s="2" t="str">
-        <f aca="false" t="array" ref="I8:I8">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E8,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J33</f>
         <v>0-0</v>
       </c>
       <c r="J8" s="2" t="str">
-        <f aca="false" t="array" ref="J8:J8">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E8,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J72</f>
         <v>5-2</v>
       </c>
       <c r="K8" s="2" t="str">
-        <f aca="false" t="array" ref="K8:K8">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E8,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J73</f>
         <v>1-0</v>
       </c>
       <c r="L8" s="2" t="str">
-        <f aca="false" t="array" ref="L8:L8">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E8,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J74</f>
         <v>2-1</v>
       </c>
       <c r="M8" s="2" t="str">
-        <f aca="false" t="array" ref="M8:M8">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E8,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J75</f>
         <v>3-1</v>
       </c>
       <c r="N8" s="2" t="str">
-        <f aca="false" t="array" ref="N8:N8">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E8,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J76</f>
         <v>0-0</v>
       </c>
       <c r="O8" s="2" t="str">
-        <f aca="false" t="array" ref="O8:O8">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E8,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J77</f>
         <v>1-0</v>
       </c>
       <c r="P8" s="2" t="str">
-        <f aca="false" t="array" ref="P8:P8">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E8,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J78</f>
         <v>2-2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -1573,47 +1573,47 @@
         <v>330</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f aca="false" t="array" ref="G9:G9">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E9,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J31</f>
         <v>2-2</v>
       </c>
       <c r="H9" s="2" t="str">
-        <f aca="false" t="array" ref="H9:H9">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E9,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J32</f>
         <v>3-2</v>
       </c>
       <c r="I9" s="2" t="str">
-        <f aca="false" t="array" ref="I9:I9">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E9,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J33</f>
         <v>0-0</v>
       </c>
       <c r="J9" s="2" t="str">
-        <f aca="false" t="array" ref="J9:J9">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E9,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J72</f>
         <v>5-2</v>
       </c>
       <c r="K9" s="2" t="str">
-        <f aca="false" t="array" ref="K9:K9">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E9,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J73</f>
         <v>1-0</v>
       </c>
       <c r="L9" s="2" t="str">
-        <f aca="false" t="array" ref="L9:L9">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E9,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J74</f>
         <v>2-1</v>
       </c>
       <c r="M9" s="2" t="str">
-        <f aca="false" t="array" ref="M9:M9">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E9,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J75</f>
         <v>3-1</v>
       </c>
       <c r="N9" s="2" t="str">
-        <f aca="false" t="array" ref="N9:N9">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E9,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J76</f>
         <v>0-0</v>
       </c>
       <c r="O9" s="2" t="str">
-        <f aca="false" t="array" ref="O9:O9">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E9,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J77</f>
         <v>1-0</v>
       </c>
       <c r="P9" s="2" t="str">
-        <f aca="false" t="array" ref="P9:P9">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E9,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J78</f>
         <v>2-2</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -1621,47 +1621,47 @@
         <v>350</v>
       </c>
       <c r="G10" s="2" t="str">
-        <f aca="false" t="array" ref="G10:G10">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E10,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J44</f>
         <v>1-0</v>
       </c>
       <c r="H10" s="2" t="str">
-        <f aca="false" t="array" ref="H10:H10">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E10,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J45</f>
         <v>5-2</v>
       </c>
       <c r="I10" s="2" t="str">
-        <f aca="false" t="array" ref="I10:I10">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E10,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J46</f>
         <v>2-0</v>
       </c>
       <c r="J10" s="2" t="str">
-        <f aca="false" t="array" ref="J10:J10">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E10,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J47</f>
         <v>3-2</v>
       </c>
       <c r="K10" s="2" t="str">
-        <f aca="false" t="array" ref="K10:K10">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E10,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J48</f>
         <v>1-0</v>
       </c>
       <c r="L10" s="2" t="str">
-        <f aca="false" t="array" ref="L10:L10">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E10,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J49</f>
         <v>1-1</v>
       </c>
       <c r="M10" s="2" t="str">
-        <f aca="false" t="array" ref="M10:M10">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E10,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J50</f>
         <v>2-2</v>
       </c>
       <c r="N10" s="2" t="str">
-        <f aca="false" t="array" ref="N10:N10">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E10,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J51</f>
         <v>0-0</v>
       </c>
       <c r="O10" s="2" t="str">
-        <f aca="false" t="array" ref="O10:O10">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E10,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J52</f>
         <v>0-0</v>
       </c>
       <c r="P10" s="2" t="str">
-        <f aca="false" t="array" ref="P10:P10">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E10,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J53</f>
         <v>2-1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -1669,47 +1669,47 @@
         <v>350</v>
       </c>
       <c r="G11" s="2" t="str">
-        <f aca="false" t="array" ref="G11:G11">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E11,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J44</f>
         <v>1-0</v>
       </c>
       <c r="H11" s="2" t="str">
-        <f aca="false" t="array" ref="H11:H11">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E11,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J45</f>
         <v>5-2</v>
       </c>
       <c r="I11" s="2" t="str">
-        <f aca="false" t="array" ref="I11:I11">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E11,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J46</f>
         <v>2-0</v>
       </c>
       <c r="J11" s="2" t="str">
-        <f aca="false" t="array" ref="J11:J11">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E11,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J47</f>
         <v>3-2</v>
       </c>
       <c r="K11" s="2" t="str">
-        <f aca="false" t="array" ref="K11:K11">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E11,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J48</f>
         <v>1-0</v>
       </c>
       <c r="L11" s="2" t="str">
-        <f aca="false" t="array" ref="L11:L11">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E11,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J49</f>
         <v>1-1</v>
       </c>
       <c r="M11" s="2" t="str">
-        <f aca="false" t="array" ref="M11:M11">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E11,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J50</f>
         <v>2-2</v>
       </c>
       <c r="N11" s="2" t="str">
-        <f aca="false" t="array" ref="N11:N11">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E11,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J51</f>
         <v>0-0</v>
       </c>
       <c r="O11" s="2" t="str">
-        <f aca="false" t="array" ref="O11:O11">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E11,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J52</f>
         <v>0-0</v>
       </c>
       <c r="P11" s="2" t="str">
-        <f aca="false" t="array" ref="P11:P11">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E11,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J53</f>
         <v>2-1</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -1717,47 +1717,47 @@
         <v>320</v>
       </c>
       <c r="G12" s="2" t="str">
-        <f aca="false" t="array" ref="G12:G12">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E12,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J30</f>
         <v>0-0</v>
       </c>
       <c r="H12" s="2" t="str">
-        <f aca="false" t="array" ref="H12:H12">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E12,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J54</f>
         <v>3-1</v>
       </c>
       <c r="I12" s="2" t="str">
-        <f aca="false" t="array" ref="I12:I12">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E12,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J55</f>
         <v>2-0</v>
       </c>
       <c r="J12" s="2" t="str">
-        <f aca="false" t="array" ref="J12:J12">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E12,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J56</f>
         <v>1-1</v>
       </c>
       <c r="K12" s="2" t="str">
-        <f aca="false" t="array" ref="K12:K12">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E12,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J57</f>
         <v>3-2</v>
       </c>
       <c r="L12" s="2" t="str">
-        <f aca="false" t="array" ref="L12:L12">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E12,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J58</f>
         <v>15-7</v>
       </c>
       <c r="M12" s="2" t="str">
-        <f aca="false" t="array" ref="M12:M12">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E12,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J59</f>
         <v>2-0</v>
       </c>
       <c r="N12" s="2" t="str">
-        <f aca="false" t="array" ref="N12:N12">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E12,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J60</f>
         <v>1-0</v>
       </c>
       <c r="O12" s="2" t="str">
-        <f aca="false" t="array" ref="O12:O12">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E12,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J61</f>
         <v>3-0</v>
       </c>
       <c r="P12" s="2" t="str">
-        <f aca="false" t="array" ref="P12:P12">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E12,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J62</f>
         <v>4-1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -1765,47 +1765,47 @@
         <v>330</v>
       </c>
       <c r="G13" s="2" t="str">
-        <f aca="false" t="array" ref="G13:G13">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E13,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J31</f>
         <v>2-2</v>
       </c>
       <c r="H13" s="2" t="str">
-        <f aca="false" t="array" ref="H13:H13">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E13,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J32</f>
         <v>3-2</v>
       </c>
       <c r="I13" s="2" t="str">
-        <f aca="false" t="array" ref="I13:I13">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E13,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J33</f>
         <v>0-0</v>
       </c>
       <c r="J13" s="2" t="str">
-        <f aca="false" t="array" ref="J13:J13">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E13,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J72</f>
         <v>5-2</v>
       </c>
       <c r="K13" s="2" t="str">
-        <f aca="false" t="array" ref="K13:K13">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E13,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J73</f>
         <v>1-0</v>
       </c>
       <c r="L13" s="2" t="str">
-        <f aca="false" t="array" ref="L13:L13">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E13,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J74</f>
         <v>2-1</v>
       </c>
       <c r="M13" s="2" t="str">
-        <f aca="false" t="array" ref="M13:M13">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E13,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J75</f>
         <v>3-1</v>
       </c>
       <c r="N13" s="2" t="str">
-        <f aca="false" t="array" ref="N13:N13">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E13,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J76</f>
         <v>0-0</v>
       </c>
       <c r="O13" s="2" t="str">
-        <f aca="false" t="array" ref="O13:O13">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E13,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J77</f>
         <v>1-0</v>
       </c>
       <c r="P13" s="2" t="str">
-        <f aca="false" t="array" ref="P13:P13">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E13,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J78</f>
         <v>2-2</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -1813,47 +1813,47 @@
         <v>330</v>
       </c>
       <c r="G14" s="2" t="str">
-        <f aca="false" t="array" ref="G14:G14">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E14,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J31</f>
         <v>2-2</v>
       </c>
       <c r="H14" s="2" t="str">
-        <f aca="false" t="array" ref="H14:H14">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E14,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J32</f>
         <v>3-2</v>
       </c>
       <c r="I14" s="2" t="str">
-        <f aca="false" t="array" ref="I14:I14">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E14,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J33</f>
         <v>0-0</v>
       </c>
       <c r="J14" s="2" t="str">
-        <f aca="false" t="array" ref="J14:J14">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E14,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J72</f>
         <v>5-2</v>
       </c>
       <c r="K14" s="2" t="str">
-        <f aca="false" t="array" ref="K14:K14">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E14,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J73</f>
         <v>1-0</v>
       </c>
       <c r="L14" s="2" t="str">
-        <f aca="false" t="array" ref="L14:L14">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E14,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J74</f>
         <v>2-1</v>
       </c>
       <c r="M14" s="2" t="str">
-        <f aca="false" t="array" ref="M14:M14">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E14,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J75</f>
         <v>3-1</v>
       </c>
       <c r="N14" s="2" t="str">
-        <f aca="false" t="array" ref="N14:N14">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E14,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J76</f>
         <v>0-0</v>
       </c>
       <c r="O14" s="2" t="str">
-        <f aca="false" t="array" ref="O14:O14">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E14,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J77</f>
         <v>1-0</v>
       </c>
       <c r="P14" s="2" t="str">
-        <f aca="false" t="array" ref="P14:P14">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E14,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J78</f>
         <v>2-2</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -1861,47 +1861,47 @@
         <v>350</v>
       </c>
       <c r="G15" s="2" t="str">
-        <f aca="false" t="array" ref="G15:G15">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E15,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J44</f>
         <v>1-0</v>
       </c>
       <c r="H15" s="2" t="str">
-        <f aca="false" t="array" ref="H15:H15">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E15,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J45</f>
         <v>5-2</v>
       </c>
       <c r="I15" s="2" t="str">
-        <f aca="false" t="array" ref="I15:I15">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E15,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J46</f>
         <v>2-0</v>
       </c>
       <c r="J15" s="2" t="str">
-        <f aca="false" t="array" ref="J15:J15">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E15,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J47</f>
         <v>3-2</v>
       </c>
       <c r="K15" s="2" t="str">
-        <f aca="false" t="array" ref="K15:K15">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E15,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J48</f>
         <v>1-0</v>
       </c>
       <c r="L15" s="2" t="str">
-        <f aca="false" t="array" ref="L15:L15">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E15,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J49</f>
         <v>1-1</v>
       </c>
       <c r="M15" s="2" t="str">
-        <f aca="false" t="array" ref="M15:M15">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E15,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J50</f>
         <v>2-2</v>
       </c>
       <c r="N15" s="2" t="str">
-        <f aca="false" t="array" ref="N15:N15">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E15,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J51</f>
         <v>0-0</v>
       </c>
       <c r="O15" s="2" t="str">
-        <f aca="false" t="array" ref="O15:O15">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E15,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J52</f>
         <v>0-0</v>
       </c>
       <c r="P15" s="2" t="str">
-        <f aca="false" t="array" ref="P15:P15">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E15,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J53</f>
         <v>2-1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -1909,47 +1909,47 @@
         <v>340</v>
       </c>
       <c r="G16" s="2" t="str">
-        <f aca="false" t="array" ref="G16:G16">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E16,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J29</f>
         <v>1-0</v>
       </c>
       <c r="H16" s="2" t="str">
-        <f aca="false" t="array" ref="H16:H16">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E16,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J63</f>
         <v>1-1</v>
       </c>
       <c r="I16" s="2" t="str">
-        <f aca="false" t="array" ref="I16:I16">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E16,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J64</f>
         <v>3-1</v>
       </c>
       <c r="J16" s="2" t="str">
-        <f aca="false" t="array" ref="J16:J16">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E16,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J65</f>
         <v>2-1</v>
       </c>
       <c r="K16" s="2" t="str">
-        <f aca="false" t="array" ref="K16:K16">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E16,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J66</f>
         <v>2-1</v>
       </c>
       <c r="L16" s="2" t="str">
-        <f aca="false" t="array" ref="L16:L16">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E16,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J67</f>
         <v>0-0</v>
       </c>
       <c r="M16" s="2" t="str">
-        <f aca="false" t="array" ref="M16:M16">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E16,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J68</f>
         <v>1-1</v>
       </c>
       <c r="N16" s="2" t="str">
-        <f aca="false" t="array" ref="N16:N16">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E16,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J69</f>
         <v>1-0</v>
       </c>
       <c r="O16" s="2" t="str">
-        <f aca="false" t="array" ref="O16:O16">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E16,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J70</f>
         <v>0-0</v>
       </c>
       <c r="P16" s="2" t="str">
-        <f aca="false" t="array" ref="P16:P16">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E16,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
-        <v>0-0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">DATI!J71</f>
+        <v>0-0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -1957,47 +1957,47 @@
         <v>320</v>
       </c>
       <c r="G17" s="2" t="str">
-        <f aca="false" t="array" ref="G17:G17">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E17,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J30</f>
         <v>0-0</v>
       </c>
       <c r="H17" s="2" t="str">
-        <f aca="false" t="array" ref="H17:H17">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E17,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J54</f>
         <v>3-1</v>
       </c>
       <c r="I17" s="2" t="str">
-        <f aca="false" t="array" ref="I17:I17">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E17,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J55</f>
         <v>2-0</v>
       </c>
       <c r="J17" s="2" t="str">
-        <f aca="false" t="array" ref="J17:J17">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E17,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J56</f>
         <v>1-1</v>
       </c>
       <c r="K17" s="2" t="str">
-        <f aca="false" t="array" ref="K17:K17">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E17,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J57</f>
         <v>3-2</v>
       </c>
       <c r="L17" s="2" t="str">
-        <f aca="false" t="array" ref="L17:L17">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E17,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J58</f>
         <v>15-7</v>
       </c>
       <c r="M17" s="2" t="str">
-        <f aca="false" t="array" ref="M17:M17">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E17,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J59</f>
         <v>2-0</v>
       </c>
       <c r="N17" s="2" t="str">
-        <f aca="false" t="array" ref="N17:N17">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E17,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J60</f>
         <v>1-0</v>
       </c>
       <c r="O17" s="2" t="str">
-        <f aca="false" t="array" ref="O17:O17">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E17,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J61</f>
         <v>3-0</v>
       </c>
       <c r="P17" s="2" t="str">
-        <f aca="false" t="array" ref="P17:P17">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E17,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J62</f>
         <v>4-1</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>44271.4166666667</v>
       </c>
@@ -2005,43 +2005,43 @@
         <v>350</v>
       </c>
       <c r="G18" s="2" t="str">
-        <f aca="false" t="array" ref="G18:G18">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E18,ROW(DATI!$J$2:$J$78)-1),G$1))</f>
+        <f aca="false">DATI!J44</f>
         <v>1-0</v>
       </c>
       <c r="H18" s="2" t="str">
-        <f aca="false" t="array" ref="H18:H18">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E18,ROW(DATI!$J$2:$J$78)-1),H$1))</f>
+        <f aca="false">DATI!J45</f>
         <v>5-2</v>
       </c>
       <c r="I18" s="2" t="str">
-        <f aca="false" t="array" ref="I18:I18">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E18,ROW(DATI!$J$2:$J$78)-1),I$1))</f>
+        <f aca="false">DATI!J46</f>
         <v>2-0</v>
       </c>
       <c r="J18" s="2" t="str">
-        <f aca="false" t="array" ref="J18:J18">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E18,ROW(DATI!$J$2:$J$78)-1),J$1))</f>
+        <f aca="false">DATI!J47</f>
         <v>3-2</v>
       </c>
       <c r="K18" s="2" t="str">
-        <f aca="false" t="array" ref="K18:K18">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E18,ROW(DATI!$J$2:$J$78)-1),K$1))</f>
+        <f aca="false">DATI!J48</f>
         <v>1-0</v>
       </c>
       <c r="L18" s="2" t="str">
-        <f aca="false" t="array" ref="L18:L18">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E18,ROW(DATI!$J$2:$J$78)-1),L$1))</f>
+        <f aca="false">DATI!J49</f>
         <v>1-1</v>
       </c>
       <c r="M18" s="2" t="str">
-        <f aca="false" t="array" ref="M18:M18">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E18,ROW(DATI!$J$2:$J$78)-1),M$1))</f>
+        <f aca="false">DATI!J50</f>
         <v>2-2</v>
       </c>
       <c r="N18" s="2" t="str">
-        <f aca="false" t="array" ref="N18:N18">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E18,ROW(DATI!$J$2:$J$78)-1),N$1))</f>
+        <f aca="false">DATI!J51</f>
         <v>0-0</v>
       </c>
       <c r="O18" s="2" t="str">
-        <f aca="false" t="array" ref="O18:O18">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E18,ROW(DATI!$J$2:$J$78)-1),O$1))</f>
+        <f aca="false">DATI!J52</f>
         <v>0-0</v>
       </c>
       <c r="P18" s="2" t="str">
-        <f aca="false" t="array" ref="P18:P18">INDEX(DATI!$J$2:$J$78,LARGE(IF(DATI!$K$2:$K$78=$E18,ROW(DATI!$J$2:$J$78)-1),P$1))</f>
+        <f aca="false">DATI!J53</f>
         <v>2-1</v>
       </c>
     </row>
